--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:12:31+00:00</t>
+    <t>2026-03-18T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}drug-mitigation:If the mitigation category is 'Drug', then only mitigation drug must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49158' implies (extension('drug').exists() and not extension('procedure').exists() and not extension('adjustment').exists())}adjustment-mitigation:If the mitigation category is 'Adjustment', then only mitigation adjustment must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49157' implies (extension('adjustment').exists() and not extension('procedure').exists() and not extension('drug').exists())}procedural-mitigation:If the mitigation category is 'Procedure', then only mitigation procedure must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49159' implies (extension('procedure').exists() and not extension('adjustment').exists() and not extension('drug').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}drug-mitigation:If the mitigation category is 'Drug', then only mitigation drug must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49158' implies (extension('drug').exists() and extension('procedure').exists().not() and extension('adjustment').exists().not())}adjustment-mitigation:If the mitigation category is 'Adjustment', then only mitigation adjustment must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49157' implies (extension('adjustment').exists() and extension('procedure').exists().not() and extension('drug').exists().not())}procedural-mitigation:If the mitigation category is 'Procedure', then only mitigation procedure must be specified. {extension('category').valueCodeableConcept.coding.code = 'C49159' implies (extension('procedure').exists() and extension('adjustment').exists().not() and extension('drug').exists().not())}</t>
   </si>
   <si>
     <t>AdverseEvent.modifierExtension</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:24:59+00:00</t>
+    <t>2026-03-31T06:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T06:24:20+00:00</t>
+    <t>2026-04-09T04:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T04:48:36+00:00</t>
+    <t>2026-04-15T07:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,7 +465,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ctcae-grade:The CTCAE grade must be between 1 and 5, inclusive. {valueInteger() &gt;= 1 and valueInteger() &lt;= 5}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ctcae-grade:The CTCAE grade must be between 1 and 5, inclusive. {valueInteger &gt;= 1 and valueInteger &lt;= 5}</t>
   </si>
   <si>
     <t>AdverseEvent.extension:resolvedDate</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:47:05+00:00</t>
+    <t>2026-04-15T19:05:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T19:05:31+00:00</t>
+    <t>2026-04-16T05:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-adverse-event.xlsx
+++ b/StructureDefinition-onconova-adverse-event.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T05:59:15+00:00</t>
+    <t>2026-04-26T18:09:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
